--- a/uncertainty_template_ipcc2019_v2.xlsx
+++ b/uncertainty_template_ipcc2019_v2.xlsx
@@ -2124,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
   <cols>
     <col width="4.6640625" customWidth="1" style="27" min="1" max="1"/>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>pct_lactating</t>
+          <t>pct_calving</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
@@ -17244,7 +17244,7 @@
     <row r="9" ht="22.05" customHeight="1" s="27">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>pct_lactating</t>
+          <t>pct_calving</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -18193,6 +18193,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="28.05" customHeight="1" s="27">
       <c r="A28" s="29" t="inlineStr">
         <is>
@@ -18275,6 +18276,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="22.05" customHeight="1" s="27">
       <c r="A35" s="28" t="inlineStr">
         <is>
@@ -18537,6 +18539,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="49"/>
     <row r="50" ht="22.05" customHeight="1" s="27">
       <c r="A50" s="28" t="inlineStr">
         <is>
@@ -18823,6 +18826,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65" ht="22.05" customHeight="1" s="27">
       <c r="A65" s="28" t="inlineStr">
         <is>
@@ -18931,7 +18935,7 @@
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>Fractions 0-1: pct_lactating, Cp</t>
+          <t>Fractions 0-1: pct_calving, Cp</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
@@ -19050,6 +19054,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77" ht="22.05" customHeight="1" s="27">
       <c r="A77" s="28" t="inlineStr">
         <is>
@@ -19373,6 +19378,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="88"/>
     <row r="89" ht="22.05" customHeight="1" s="27">
       <c r="A89" s="28" t="inlineStr">
         <is>
@@ -19680,13 +19686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B616C8EB-85D0-4778-9635-F35064684CF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1EFF87C-D9F3-471B-84D3-2FFECE5A359F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC6721C-ABA5-453E-87C7-992E3DF2FD23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F81591-7447-41C6-8BBF-3D8CEF7A30EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE9FB51A-7284-4D5C-AD1F-A4D0558C3EAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B96DDB4-7A00-49BB-8C8B-04AC9E48CE8A}"/>
 </file>